--- a/en/downloads/data-excel/17.13.1.1.xlsx
+++ b/en/downloads/data-excel/17.13.1.1.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B884609F-C35B-401A-87E6-B1A3058CBF8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -109,8 +110,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="10" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -175,6 +176,11 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -217,30 +223,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -252,25 +258,32 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 2" xfId="1"/>
+    <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -286,9 +299,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -326,9 +339,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -363,7 +376,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -398,7 +411,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -571,8 +584,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:S14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="37.85546875" customWidth="1"/>
@@ -582,7 +595,7 @@
     <col min="12" max="12" width="9.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -602,7 +615,7 @@
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
     </row>
-    <row r="2" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -615,8 +628,10 @@
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
-    </row>
-    <row r="3" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R2" s="15"/>
+      <c r="S2" s="15"/>
+    </row>
+    <row r="3" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
@@ -668,8 +683,14 @@
       <c r="Q3" s="8">
         <v>2023</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R3" s="16">
+        <v>2024</v>
+      </c>
+      <c r="S3" s="16">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>5</v>
       </c>
@@ -679,50 +700,54 @@
       <c r="C4" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="13">
         <v>99.5</v>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="13">
         <v>106</v>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="13">
         <v>99.9</v>
       </c>
-      <c r="G4" s="14">
+      <c r="G4" s="13">
         <v>110.9</v>
       </c>
-      <c r="H4" s="14">
+      <c r="H4" s="13">
         <v>104</v>
       </c>
-      <c r="I4" s="14">
+      <c r="I4" s="13">
         <v>103.9</v>
       </c>
-      <c r="J4" s="14">
+      <c r="J4" s="13">
         <v>104.3</v>
       </c>
-      <c r="K4" s="14">
+      <c r="K4" s="13">
         <v>104.7</v>
       </c>
-      <c r="L4" s="14">
+      <c r="L4" s="13">
         <v>103.8</v>
       </c>
-      <c r="M4" s="14">
+      <c r="M4" s="13">
         <v>104.6</v>
       </c>
-      <c r="N4" s="14">
+      <c r="N4" s="13">
         <v>92.9</v>
       </c>
-      <c r="O4" s="14">
+      <c r="O4" s="13">
         <v>105.5</v>
       </c>
-      <c r="P4" s="14">
+      <c r="P4" s="13">
         <v>109</v>
       </c>
-      <c r="Q4" s="14">
+      <c r="Q4" s="13">
         <v>109</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R4" s="17">
+        <v>111.5</v>
+      </c>
+      <c r="S4" s="17"/>
+    </row>
+    <row r="5" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>9</v>
       </c>
@@ -732,50 +757,56 @@
       <c r="C5" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="13">
         <v>108</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="13">
         <v>116.6</v>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="13">
         <v>102.8</v>
       </c>
-      <c r="G5" s="14">
+      <c r="G5" s="13">
         <v>106.6</v>
       </c>
-      <c r="H5" s="14">
+      <c r="H5" s="13">
         <v>107.5</v>
       </c>
-      <c r="I5" s="14">
+      <c r="I5" s="13">
         <v>106.5</v>
       </c>
-      <c r="J5" s="14">
+      <c r="J5" s="13">
         <v>100.4</v>
       </c>
-      <c r="K5" s="14">
+      <c r="K5" s="13">
         <v>103.2</v>
       </c>
-      <c r="L5" s="14">
+      <c r="L5" s="13">
         <v>101.5</v>
       </c>
-      <c r="M5" s="14">
+      <c r="M5" s="13">
         <v>101.1</v>
       </c>
-      <c r="N5" s="14">
+      <c r="N5" s="13">
         <v>106.3</v>
       </c>
-      <c r="O5" s="14">
+      <c r="O5" s="13">
         <v>111.90503981851454</v>
       </c>
-      <c r="P5" s="14">
+      <c r="P5" s="13">
         <v>113.92290931741762</v>
       </c>
-      <c r="Q5" s="14">
+      <c r="Q5" s="13">
         <v>110.8</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R5" s="17">
+        <v>106.3</v>
+      </c>
+      <c r="S5" s="17">
+        <v>109.4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>10</v>
       </c>
@@ -785,50 +816,56 @@
       <c r="C6" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="13">
         <v>122.79</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="13">
         <v>122.02</v>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="13">
         <v>105.3</v>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="13">
         <v>97.92</v>
       </c>
-      <c r="H6" s="14">
+      <c r="H6" s="13">
         <v>101.45</v>
       </c>
-      <c r="I6" s="14">
+      <c r="I6" s="13">
         <v>108.75</v>
       </c>
-      <c r="J6" s="14">
+      <c r="J6" s="13">
         <v>106.41</v>
       </c>
-      <c r="K6" s="14">
+      <c r="K6" s="13">
         <v>101.66</v>
       </c>
-      <c r="L6" s="14">
+      <c r="L6" s="13">
         <v>101.49</v>
       </c>
-      <c r="M6" s="14">
+      <c r="M6" s="13">
         <v>104.26</v>
       </c>
-      <c r="N6" s="14">
+      <c r="N6" s="13">
         <v>121.27</v>
       </c>
-      <c r="O6" s="14">
+      <c r="O6" s="13">
         <v>111.5</v>
       </c>
-      <c r="P6" s="14">
+      <c r="P6" s="13">
         <v>105.1</v>
       </c>
-      <c r="Q6" s="14">
+      <c r="Q6" s="13">
         <v>109.3</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R6" s="17">
+        <v>113.5</v>
+      </c>
+      <c r="S6" s="17">
+        <v>125.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
         <v>13</v>
       </c>
@@ -838,50 +875,54 @@
       <c r="C7" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="13">
         <v>-10767.9787</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="13">
         <v>-13663.7111</v>
       </c>
-      <c r="F7" s="14">
+      <c r="F7" s="13">
         <v>-20232.313399999999</v>
       </c>
-      <c r="G7" s="14">
+      <c r="G7" s="13">
         <v>-2330.4822999999997</v>
       </c>
-      <c r="H7" s="14">
+      <c r="H7" s="13">
         <v>-1875.5431000000001</v>
       </c>
-      <c r="I7" s="14">
+      <c r="I7" s="13">
         <v>-6149.3212999999996</v>
       </c>
-      <c r="J7" s="14">
+      <c r="J7" s="13">
         <v>-20888.912399999997</v>
       </c>
-      <c r="K7" s="14">
+      <c r="K7" s="13">
         <v>-16476.160199999998</v>
       </c>
-      <c r="L7" s="14">
+      <c r="L7" s="13">
         <v>-6188.9007999999994</v>
       </c>
-      <c r="M7" s="14">
+      <c r="M7" s="13">
         <v>-431.70920000000001</v>
       </c>
-      <c r="N7" s="14">
+      <c r="N7" s="13">
         <v>-19734.036599999999</v>
       </c>
-      <c r="O7" s="14">
+      <c r="O7" s="13">
         <v>-1763.6</v>
       </c>
-      <c r="P7" s="14">
+      <c r="P7" s="13">
         <v>-10400.700000000001</v>
       </c>
-      <c r="Q7" s="14">
+      <c r="Q7" s="13">
         <v>12685.1</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R7" s="17">
+        <v>37650.800000000003</v>
+      </c>
+      <c r="S7" s="17"/>
+    </row>
+    <row r="8" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>14</v>
       </c>
@@ -891,50 +932,54 @@
       <c r="C8" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="13">
         <v>7667.4054999999998</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="13">
         <v>9394.6681489399998</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="13">
         <v>11440.610560159999</v>
       </c>
-      <c r="G8" s="14">
+      <c r="G8" s="13">
         <v>13939.585690450001</v>
       </c>
-      <c r="H8" s="14">
+      <c r="H8" s="13">
         <v>13713.456934360001</v>
       </c>
-      <c r="I8" s="14">
+      <c r="I8" s="13">
         <v>14364.393600000001</v>
       </c>
-      <c r="J8" s="14">
+      <c r="J8" s="13">
         <v>20698.734024999998</v>
       </c>
-      <c r="K8" s="14">
+      <c r="K8" s="13">
         <v>20620.480819839999</v>
       </c>
-      <c r="L8" s="14">
+      <c r="L8" s="13">
         <v>23747.690011019997</v>
       </c>
-      <c r="M8" s="14">
+      <c r="M8" s="13">
         <v>319474.59999999998</v>
       </c>
-      <c r="N8" s="14">
+      <c r="N8" s="13">
         <v>407116.85000000003</v>
       </c>
-      <c r="O8" s="14">
+      <c r="O8" s="13">
         <v>436586.8</v>
       </c>
-      <c r="P8" s="14">
+      <c r="P8" s="13">
         <v>478225.6</v>
       </c>
-      <c r="Q8" s="14">
+      <c r="Q8" s="13">
         <v>559503.6</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" ht="24" x14ac:dyDescent="0.25">
+      <c r="R8" s="18">
+        <v>573267</v>
+      </c>
+      <c r="S8" s="18"/>
+    </row>
+    <row r="9" spans="1:19" ht="24" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>16</v>
       </c>
@@ -944,156 +989,168 @@
       <c r="C9" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="13">
         <v>105.6</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="13">
         <v>130.62446020045391</v>
       </c>
-      <c r="F9" s="14">
+      <c r="F9" s="13">
         <v>115.38426054064028</v>
       </c>
-      <c r="G9" s="14">
+      <c r="G9" s="13">
         <v>106.52860512533483</v>
       </c>
-      <c r="H9" s="14">
+      <c r="H9" s="13">
         <v>95.303860491881196</v>
       </c>
-      <c r="I9" s="14">
+      <c r="I9" s="13">
         <v>73.989322482411012</v>
       </c>
-      <c r="J9" s="14">
+      <c r="J9" s="13">
         <v>98.878751854324321</v>
       </c>
-      <c r="K9" s="14">
+      <c r="K9" s="13">
         <v>112.29725850437777</v>
       </c>
-      <c r="L9" s="14">
+      <c r="L9" s="13">
         <v>113.89678862438089</v>
       </c>
-      <c r="M9" s="14">
+      <c r="M9" s="13">
         <v>97.8</v>
       </c>
-      <c r="N9" s="14">
+      <c r="N9" s="13">
         <v>81.599999999999994</v>
       </c>
-      <c r="O9" s="14">
+      <c r="O9" s="13">
         <v>146.4</v>
       </c>
-      <c r="P9" s="14">
+      <c r="P9" s="13">
         <v>144.69999999999999</v>
       </c>
-      <c r="Q9" s="14">
+      <c r="Q9" s="13">
         <v>131.9</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
+      <c r="R9" s="17">
+        <v>110.9</v>
+      </c>
+      <c r="S9" s="15"/>
+    </row>
+    <row r="10" spans="1:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="15">
+      <c r="D10" s="13">
         <v>1755.9245000000001</v>
       </c>
-      <c r="E10" s="15">
+      <c r="E10" s="13">
         <v>2242.1664000000001</v>
       </c>
-      <c r="F10" s="15">
+      <c r="F10" s="13">
         <v>1927.6232</v>
       </c>
-      <c r="G10" s="15">
+      <c r="G10" s="13">
         <v>2006.8497</v>
       </c>
-      <c r="H10" s="15">
+      <c r="H10" s="13">
         <v>1883.7334559999999</v>
       </c>
-      <c r="I10" s="15">
+      <c r="I10" s="13">
         <v>1482.9420339999999</v>
       </c>
-      <c r="J10" s="15">
+      <c r="J10" s="13">
         <v>1573.2149299999999</v>
       </c>
-      <c r="K10" s="15">
+      <c r="K10" s="13">
         <v>1764.2546440000001</v>
       </c>
-      <c r="L10" s="15">
+      <c r="L10" s="13">
         <v>1836.838696</v>
       </c>
-      <c r="M10" s="15">
+      <c r="M10" s="13">
         <v>1986.11</v>
       </c>
-      <c r="N10" s="15">
+      <c r="N10" s="13">
         <v>1973.2</v>
       </c>
-      <c r="O10" s="15">
+      <c r="O10" s="13">
         <v>2752.1</v>
       </c>
-      <c r="P10" s="15">
+      <c r="P10" s="13">
         <v>2254.6999999999998</v>
       </c>
-      <c r="Q10" s="15">
+      <c r="Q10" s="13">
         <v>3384.8</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="13" t="s">
+      <c r="R10" s="17">
+        <v>5141.7</v>
+      </c>
+      <c r="S10" s="15"/>
+    </row>
+    <row r="11" spans="1:19" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="16">
+      <c r="D11" s="14">
         <v>3222.7721820000002</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="14">
         <v>4261.2264179999993</v>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="14">
         <v>5576.2641309999999</v>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="14">
         <v>5986.9830029999994</v>
       </c>
-      <c r="H11" s="16">
+      <c r="H11" s="14">
         <v>5734.7038080000002</v>
       </c>
-      <c r="I11" s="16">
+      <c r="I11" s="14">
         <v>4153.8605099999995</v>
       </c>
-      <c r="J11" s="16">
+      <c r="J11" s="14">
         <v>4000.4421069999999</v>
       </c>
-      <c r="K11" s="16">
+      <c r="K11" s="14">
         <v>4494.7281780000003</v>
       </c>
-      <c r="L11" s="16">
+      <c r="L11" s="14">
         <v>5291.9457759999996</v>
       </c>
-      <c r="M11" s="16">
+      <c r="M11" s="14">
         <v>4989.01</v>
       </c>
-      <c r="N11" s="16">
+      <c r="N11" s="14">
         <v>3718.8</v>
       </c>
-      <c r="O11" s="16">
+      <c r="O11" s="14">
         <v>5580.2</v>
       </c>
-      <c r="P11" s="16">
+      <c r="P11" s="14">
         <v>9803.2000000000007</v>
       </c>
-      <c r="Q11" s="16">
+      <c r="Q11" s="14">
         <v>12517.9</v>
       </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R11" s="19">
+        <v>12489.3</v>
+      </c>
+      <c r="S11" s="19"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="10"/>
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
@@ -1108,7 +1165,7 @@
       <c r="L12" s="11"/>
       <c r="M12" s="11"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="10"/>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
@@ -1123,7 +1180,7 @@
       <c r="L13" s="11"/>
       <c r="M13" s="11"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="10"/>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
